--- a/Shablon/34401A.xlsx
+++ b/Shablon/34401A.xlsx
@@ -19,16 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="131">
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="126">
   <si>
     <t>Условия проведения калибровки:</t>
   </si>
@@ -472,12 +463,6 @@
   </si>
   <si>
     <t>+</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -936,22 +921,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -966,41 +988,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1009,60 +1019,35 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1376,81 +1361,71 @@
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
     <col min="2" max="3" width="11.7109375" style="3" customWidth="1"/>
     <col min="4" max="8" width="10.7109375" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="86"/>
+    <col min="9" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
+      <c r="A1" s="67"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="87" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="76" t="str">
+      <c r="A7" s="85" t="str">
         <f>"Протокол поверки № 10/"&amp;C101&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1463,29 +1438,29 @@
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
+      <c r="A9" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E9" s="36"/>
-      <c r="F9" s="88" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="88"/>
+      <c r="F9" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="55"/>
       <c r="H9" s="37"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="89" t="s">
-        <v>34</v>
+      <c r="A10" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="56" t="s">
+        <v>31</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -1493,11 +1468,11 @@
       <c r="H10" s="37"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
+      <c r="A11" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="35"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
@@ -1505,13 +1480,13 @@
       <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
+      <c r="A12" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
@@ -1519,13 +1494,13 @@
       <c r="H12" s="37"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="89" t="s">
-        <v>92</v>
+      <c r="A13" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="56" t="s">
+        <v>89</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1533,13 +1508,13 @@
       <c r="H13" s="37"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="39" t="s">
         <v>84</v>
-      </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="39" t="s">
-        <v>87</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -1547,13 +1522,13 @@
       <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
+      <c r="A15" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
@@ -1563,99 +1538,99 @@
     <row r="16" spans="1:8" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79" t="s">
+      <c r="E18" s="81"/>
+      <c r="F18" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="81"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="82"/>
+      <c r="F19" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="81"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="82"/>
+      <c r="F20" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="81"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="83" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="82"/>
+      <c r="F21" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="81"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="79"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="78" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79" t="s">
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="79"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="78"/>
-      <c r="F20" s="79" t="s">
+      <c r="G22" s="81"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="79"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="78"/>
-      <c r="F21" s="79" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="79"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="79"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="79"/>
+      <c r="G23" s="81"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1670,7 +1645,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -1692,17 +1667,17 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1714,7 +1689,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1725,50 +1700,50 @@
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="65"/>
+      <c r="A31" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="74"/>
+      <c r="D31" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="93"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="76"/>
       <c r="F32" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="66" t="s">
-        <v>109</v>
+      <c r="A33" s="63" t="s">
+        <v>106</v>
       </c>
       <c r="B33" s="51">
         <v>100</v>
       </c>
-      <c r="C33" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="54" t="s">
-        <v>106</v>
+      <c r="C33" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>103</v>
       </c>
       <c r="F33" s="42">
         <f>100-0.0085</f>
@@ -1780,15 +1755,15 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="51">
         <v>-100</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="55"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="72"/>
       <c r="F34" s="42">
         <f>-100-0.0085</f>
         <v>-100.0085</v>
@@ -1799,20 +1774,20 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66" t="s">
-        <v>110</v>
+      <c r="A35" s="63" t="s">
+        <v>107</v>
       </c>
       <c r="B35" s="51">
         <v>1</v>
       </c>
-      <c r="C35" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="90" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="57" t="s">
-        <v>107</v>
+      <c r="C35" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="94" t="s">
+        <v>104</v>
       </c>
       <c r="F35" s="45">
         <f>1-0.000047</f>
@@ -1824,15 +1799,15 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="66"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="51">
         <v>-1</v>
       </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="90" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="58"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="95"/>
       <c r="F36" s="44">
         <f>-1-0.000047</f>
         <v>-1.0000469999999999</v>
@@ -1843,17 +1818,17 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="66" t="s">
-        <v>111</v>
+      <c r="A37" s="63" t="s">
+        <v>108</v>
       </c>
       <c r="B37" s="51">
         <v>10</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="58"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="95"/>
       <c r="F37" s="42">
         <f>10-0.0004</f>
         <v>9.9995999999999992</v>
@@ -1864,15 +1839,15 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="66"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="51">
         <v>-10</v>
       </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="90" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="58"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="95"/>
       <c r="F38" s="42">
         <f>-10-0.0004</f>
         <v>-10.000400000000001</v>
@@ -1883,17 +1858,17 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="66" t="s">
-        <v>112</v>
+      <c r="A39" s="63" t="s">
+        <v>109</v>
       </c>
       <c r="B39" s="51">
         <v>100</v>
       </c>
-      <c r="C39" s="56"/>
-      <c r="D39" s="90" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="58"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="95"/>
       <c r="F39" s="42">
         <f>100-0.0051</f>
         <v>99.994900000000001</v>
@@ -1904,15 +1879,15 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="66"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="51">
         <v>-100</v>
       </c>
-      <c r="C40" s="56"/>
-      <c r="D40" s="90" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="58"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="95"/>
       <c r="F40" s="42">
         <f>-100-0.0051</f>
         <v>-100.0051</v>
@@ -1923,17 +1898,17 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="72" t="s">
-        <v>113</v>
+      <c r="A41" s="87" t="s">
+        <v>110</v>
       </c>
       <c r="B41" s="51">
         <v>1000</v>
       </c>
-      <c r="C41" s="56"/>
-      <c r="D41" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="58"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="95"/>
       <c r="F41" s="43">
         <f>1000-0.055</f>
         <v>999.94500000000005</v>
@@ -1944,15 +1919,15 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="72"/>
+      <c r="A42" s="87"/>
       <c r="B42" s="51">
         <v>-1000</v>
       </c>
-      <c r="C42" s="55"/>
-      <c r="D42" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="59"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="96"/>
       <c r="F42" s="43">
         <f>-1000-0.055</f>
         <v>-1000.0549999999999</v>
@@ -1964,7 +1939,7 @@
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1975,57 +1950,57 @@
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B45" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="61"/>
-      <c r="D45" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="61"/>
-      <c r="G45" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" s="65"/>
+      <c r="A45" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="74"/>
+      <c r="D45" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="74"/>
+      <c r="G45" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="93"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66"/>
-      <c r="B46" s="62"/>
-      <c r="C46" s="63"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="63"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="76"/>
       <c r="G46" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H46" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="75" t="s">
-        <v>109</v>
+      <c r="A47" s="65" t="s">
+        <v>106</v>
       </c>
       <c r="B47" s="53">
         <v>10</v>
       </c>
-      <c r="C47" s="75" t="s">
-        <v>106</v>
+      <c r="C47" s="65" t="s">
+        <v>103</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" s="75" t="s">
-        <v>106</v>
+        <v>11</v>
+      </c>
+      <c r="E47" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" s="65" t="s">
+        <v>103</v>
       </c>
       <c r="G47" s="43">
         <f>10-0.046</f>
@@ -2037,18 +2012,18 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="73"/>
-      <c r="B48" s="75">
+      <c r="A48" s="78"/>
+      <c r="B48" s="65">
         <v>100</v>
       </c>
-      <c r="C48" s="73"/>
+      <c r="C48" s="78"/>
       <c r="D48" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" s="73"/>
+        <v>11</v>
+      </c>
+      <c r="E48" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" s="78"/>
       <c r="G48" s="51">
         <f>100-0.1</f>
         <v>99.9</v>
@@ -2059,16 +2034,16 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="74"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="74"/>
+      <c r="A49" s="66"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
       <c r="D49" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" s="92" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="74"/>
+        <v>13</v>
+      </c>
+      <c r="E49" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="F49" s="66"/>
       <c r="G49" s="10">
         <f>100-0.17</f>
         <v>99.83</v>
@@ -2079,23 +2054,23 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="71">
+      <c r="A50" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="80">
         <v>1</v>
       </c>
-      <c r="C50" s="75" t="s">
-        <v>107</v>
+      <c r="C50" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="D50" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="92" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="75" t="s">
-        <v>107</v>
+        <v>11</v>
+      </c>
+      <c r="E50" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="G50" s="42">
         <f>1-0.0001</f>
@@ -2107,16 +2082,16 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="84"/>
-      <c r="B51" s="71"/>
-      <c r="C51" s="74"/>
+      <c r="A51" s="79"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="66"/>
       <c r="D51" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="74"/>
+        <v>13</v>
+      </c>
+      <c r="E51" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="66"/>
       <c r="G51" s="42">
         <f>1-0.0017</f>
         <v>0.99829999999999997</v>
@@ -2130,62 +2105,62 @@
       <c r="A52" s="41"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="93"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
       <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="74"/>
+      <c r="D53" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="F53" s="74"/>
+      <c r="G53" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="H53" s="93"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="63"/>
+      <c r="B54" s="75"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" s="49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="61"/>
-      <c r="D53" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="E53" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="F53" s="61"/>
-      <c r="G53" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="H53" s="65"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="66"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="66"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="H54" s="49" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="B55" s="73">
+      <c r="B55" s="78">
         <v>10</v>
       </c>
-      <c r="C55" s="75" t="s">
-        <v>107</v>
+      <c r="C55" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" s="75" t="s">
-        <v>107</v>
+        <v>12</v>
+      </c>
+      <c r="E55" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="G55" s="52">
         <f>10-0.009</f>
@@ -2197,16 +2172,16 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="73"/>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
+      <c r="A56" s="78"/>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
       <c r="D56" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="92" t="s">
-        <v>57</v>
-      </c>
-      <c r="F56" s="73"/>
+        <v>11</v>
+      </c>
+      <c r="E56" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="F56" s="78"/>
       <c r="G56" s="43">
         <f>10-0.009</f>
         <v>9.9909999999999997</v>
@@ -2217,16 +2192,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="73"/>
+      <c r="A57" s="66"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="78"/>
       <c r="D57" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" s="92" t="s">
-        <v>58</v>
-      </c>
-      <c r="F57" s="73"/>
+        <v>13</v>
+      </c>
+      <c r="E57" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="78"/>
       <c r="G57" s="43">
         <f>10-0.017</f>
         <v>9.9830000000000005</v>
@@ -2237,20 +2212,20 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="75" t="s">
-        <v>112</v>
-      </c>
-      <c r="B58" s="75">
+      <c r="A58" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="65">
         <v>100</v>
       </c>
-      <c r="C58" s="73"/>
+      <c r="C58" s="78"/>
       <c r="D58" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="F58" s="73"/>
+        <v>11</v>
+      </c>
+      <c r="E58" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" s="78"/>
       <c r="G58" s="10">
         <f>100-0.09</f>
         <v>99.91</v>
@@ -2261,16 +2236,16 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
-      <c r="C59" s="73"/>
+      <c r="A59" s="66"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="78"/>
       <c r="D59" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" s="73"/>
+        <v>13</v>
+      </c>
+      <c r="E59" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="F59" s="78"/>
       <c r="G59" s="10">
         <f>100-0.17</f>
         <v>99.83</v>
@@ -2281,20 +2256,20 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="75">
+      <c r="A60" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="65">
         <v>750</v>
       </c>
-      <c r="C60" s="73"/>
+      <c r="C60" s="78"/>
       <c r="D60" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="90" t="s">
-        <v>61</v>
-      </c>
-      <c r="F60" s="73"/>
+        <v>11</v>
+      </c>
+      <c r="E60" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="F60" s="78"/>
       <c r="G60" s="43">
         <f>750-0.625</f>
         <v>749.375</v>
@@ -2305,16 +2280,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="74"/>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
+      <c r="A61" s="66"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="66"/>
       <c r="D61" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="90" t="s">
-        <v>62</v>
-      </c>
-      <c r="F61" s="74"/>
+        <v>13</v>
+      </c>
+      <c r="E61" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="66"/>
       <c r="G61" s="43">
         <f>750-1.275</f>
         <v>748.72500000000002</v>
@@ -2334,7 +2309,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="13"/>
@@ -2343,50 +2318,50 @@
       <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" s="61"/>
-      <c r="F64" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G64" s="65"/>
+      <c r="A64" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B64" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="74"/>
+      <c r="D64" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E64" s="74"/>
+      <c r="F64" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G64" s="93"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="62"/>
-      <c r="C65" s="63"/>
-      <c r="D65" s="62"/>
-      <c r="E65" s="63"/>
+      <c r="A65" s="63"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="76"/>
       <c r="F65" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G65" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="53" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B66" s="53">
         <v>10</v>
       </c>
-      <c r="C66" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" s="92" t="s">
-        <v>63</v>
-      </c>
-      <c r="E66" s="67" t="s">
-        <v>104</v>
+      <c r="C66" s="71" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" s="88" t="s">
+        <v>101</v>
       </c>
       <c r="F66" s="43">
         <f>10-0.007</f>
@@ -2399,16 +2374,16 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B67" s="53">
         <v>100</v>
       </c>
-      <c r="C67" s="55"/>
-      <c r="D67" s="92" t="s">
-        <v>64</v>
-      </c>
-      <c r="E67" s="68"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="E67" s="89"/>
       <c r="F67" s="43">
         <f>100-0.055</f>
         <v>99.944999999999993</v>
@@ -2420,19 +2395,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="53" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B68" s="53">
         <v>1</v>
       </c>
-      <c r="C68" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" s="92" t="s">
-        <v>65</v>
-      </c>
-      <c r="E68" s="67" t="s">
-        <v>105</v>
+      <c r="C68" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="88" t="s">
+        <v>102</v>
       </c>
       <c r="F68" s="42">
         <f>1-0.0011</f>
@@ -2445,16 +2420,16 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="53" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B69" s="53">
         <v>2</v>
       </c>
-      <c r="C69" s="55"/>
-      <c r="D69" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="E69" s="68"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" s="89"/>
       <c r="F69" s="43">
         <f>2-0.003</f>
         <v>1.9970000000000001</v>
@@ -2474,7 +2449,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="13"/>
@@ -2483,52 +2458,52 @@
       <c r="F71" s="16"/>
     </row>
     <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B72" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E72" s="61"/>
-      <c r="F72" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G72" s="65"/>
+      <c r="A72" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72" s="74"/>
+      <c r="F72" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G72" s="93"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="82"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="62"/>
-      <c r="E73" s="63"/>
+      <c r="A73" s="63"/>
+      <c r="B73" s="64"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="76"/>
       <c r="F73" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G73" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B74" s="53">
         <v>1</v>
       </c>
-      <c r="C74" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="E74" s="67" t="s">
-        <v>105</v>
+      <c r="C74" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="88" t="s">
+        <v>102</v>
       </c>
       <c r="F74" s="42">
         <f>1-0.0014</f>
@@ -2541,16 +2516,16 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="53" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B75" s="53">
         <v>2</v>
       </c>
-      <c r="C75" s="71"/>
-      <c r="D75" s="92" t="s">
-        <v>68</v>
-      </c>
-      <c r="E75" s="68"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="89"/>
       <c r="F75" s="42">
         <f>2-0.0048</f>
         <v>1.9952000000000001</v>
@@ -2570,7 +2545,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
@@ -2579,57 +2554,57 @@
       <c r="F77" s="16"/>
     </row>
     <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B78" s="82" t="s">
-        <v>102</v>
-      </c>
-      <c r="C78" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="61"/>
-      <c r="E78" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="F78" s="61"/>
-      <c r="G78" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="H78" s="65"/>
+      <c r="A78" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="74"/>
+      <c r="E78" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="F78" s="74"/>
+      <c r="G78" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="H78" s="93"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="82"/>
-      <c r="C79" s="69"/>
-      <c r="D79" s="70"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="63"/>
+      <c r="A79" s="63"/>
+      <c r="B79" s="64"/>
+      <c r="C79" s="90"/>
+      <c r="D79" s="91"/>
+      <c r="E79" s="75"/>
+      <c r="F79" s="76"/>
       <c r="G79" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H79" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="49" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B80" s="49" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C80" s="22">
         <v>100</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="E80" s="90" t="s">
-        <v>69</v>
+        <v>94</v>
+      </c>
+      <c r="E80" s="57" t="s">
+        <v>66</v>
       </c>
       <c r="F80" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G80" s="51">
         <f>100-0.1</f>
@@ -2642,22 +2617,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="49" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B81" s="49" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C81" s="22">
         <v>100</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" s="90" t="s">
-        <v>70</v>
+        <v>95</v>
+      </c>
+      <c r="E81" s="57" t="s">
+        <v>67</v>
       </c>
       <c r="F81" s="40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G81" s="10">
         <f>100-0.01</f>
@@ -2678,7 +2653,7 @@
     </row>
     <row r="83" spans="1:8" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
@@ -2688,7 +2663,7 @@
     </row>
     <row r="84" spans="1:8" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -2697,50 +2672,50 @@
       <c r="F84" s="21"/>
     </row>
     <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B85" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C85" s="61"/>
-      <c r="D85" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="61"/>
-      <c r="F85" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G85" s="65"/>
+      <c r="A85" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" s="74"/>
+      <c r="D85" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E85" s="74"/>
+      <c r="F85" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G85" s="93"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="62"/>
-      <c r="C86" s="63"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="63"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="76"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="76"/>
       <c r="F86" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G86" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B87" s="22">
         <v>100</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D87" s="90" t="s">
-        <v>71</v>
+        <v>96</v>
+      </c>
+      <c r="D87" s="57" t="s">
+        <v>68</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F87" s="43">
         <f>100-0.014</f>
@@ -2753,19 +2728,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B88" s="22">
         <v>1</v>
       </c>
-      <c r="C88" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="D88" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="E88" s="54" t="s">
-        <v>100</v>
+      <c r="C88" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="71" t="s">
+        <v>97</v>
       </c>
       <c r="F88" s="42">
         <f>1-0.0001</f>
@@ -2778,16 +2753,16 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B89" s="22">
         <v>10</v>
       </c>
-      <c r="C89" s="56"/>
-      <c r="D89" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="E89" s="56"/>
+      <c r="C89" s="77"/>
+      <c r="D89" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="77"/>
       <c r="F89" s="42">
         <f>10-0.0011</f>
         <v>9.9989000000000008</v>
@@ -2799,16 +2774,16 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B90" s="22">
         <v>100</v>
       </c>
-      <c r="C90" s="55"/>
-      <c r="D90" s="90" t="s">
-        <v>74</v>
-      </c>
-      <c r="E90" s="55"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E90" s="72"/>
       <c r="F90" s="43">
         <f>100-0.011</f>
         <v>99.989000000000004</v>
@@ -2828,7 +2803,7 @@
     </row>
     <row r="92" spans="1:8" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A92" s="28" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -2837,50 +2812,50 @@
       <c r="F92" s="21"/>
     </row>
     <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B93" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C93" s="61"/>
-      <c r="D93" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E93" s="61"/>
-      <c r="F93" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B93" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" s="74"/>
+      <c r="D93" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E93" s="74"/>
+      <c r="F93" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G93" s="93"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="69"/>
-      <c r="C94" s="70"/>
-      <c r="D94" s="62"/>
-      <c r="E94" s="63"/>
+      <c r="A94" s="63"/>
+      <c r="B94" s="90"/>
+      <c r="C94" s="91"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="76"/>
       <c r="F94" s="49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G94" s="49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B95" s="22">
         <v>1</v>
       </c>
-      <c r="C95" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="D95" s="90" t="s">
-        <v>75</v>
-      </c>
-      <c r="E95" s="54" t="s">
-        <v>101</v>
+      <c r="C95" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E95" s="71" t="s">
+        <v>98</v>
       </c>
       <c r="F95" s="44">
         <f>1-0.00011</f>
@@ -2893,16 +2868,16 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B96" s="22">
         <v>10</v>
       </c>
-      <c r="C96" s="56"/>
-      <c r="D96" s="90" t="s">
-        <v>76</v>
-      </c>
-      <c r="E96" s="56"/>
+      <c r="C96" s="77"/>
+      <c r="D96" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E96" s="77"/>
       <c r="F96" s="42">
         <f>10-0.0041</f>
         <v>9.9959000000000007</v>
@@ -2914,16 +2889,16 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B97" s="22">
         <v>100</v>
       </c>
-      <c r="C97" s="55"/>
-      <c r="D97" s="90" t="s">
-        <v>77</v>
-      </c>
-      <c r="E97" s="55"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="E97" s="72"/>
       <c r="F97" s="10">
         <f>100-0.81</f>
         <v>99.19</v>
@@ -2942,47 +2917,130 @@
       <c r="F98" s="16"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="B99" s="81"/>
+      <c r="A99" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="B99" s="62"/>
       <c r="C99" s="48" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="F99" s="16"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B100" s="81"/>
+      <c r="A100" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B100" s="62"/>
       <c r="C100" s="30"/>
       <c r="D100" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="95" t="s">
-        <v>38</v>
-      </c>
-      <c r="F100" s="83"/>
+        <v>9</v>
+      </c>
+      <c r="E100" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="F100" s="70"/>
       <c r="G100" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H100" s="32"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="B101" s="81"/>
-      <c r="C101" s="96" t="s">
-        <v>39</v>
-      </c>
-      <c r="D101" s="96"/>
+      <c r="A101" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="62"/>
+      <c r="C101" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="107">
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="E35:E42"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B53:C54"/>
+    <mergeCell ref="C55:C61"/>
+    <mergeCell ref="F55:F61"/>
+    <mergeCell ref="E53:F54"/>
+    <mergeCell ref="B45:C46"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="E45:F46"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="E78:F79"/>
+    <mergeCell ref="D85:E86"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="D72:E73"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:E65"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="D93:E94"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="B93:C94"/>
+    <mergeCell ref="C95:C97"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B31:C32"/>
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A101:B101"/>
@@ -3007,89 +3065,6 @@
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:E65"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="D93:E94"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="B93:C94"/>
-    <mergeCell ref="C95:C97"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="E78:F79"/>
-    <mergeCell ref="D85:E86"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="D72:E73"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="E35:E42"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B53:C54"/>
-    <mergeCell ref="C55:C61"/>
-    <mergeCell ref="F55:F61"/>
-    <mergeCell ref="E53:F54"/>
-    <mergeCell ref="B45:C46"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="E45:F46"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G53:H53"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.61458333333333337" header="0.39370078740157483" footer="0.39370078740157483"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
